--- a/06_Office_Related/01_NSO_work/06_SL_to_PIVOT_to_Compare_with_WP/02_GJ_WP_2026-27/SL 2.0/BOTAD.xlsx
+++ b/06_Office_Related/01_NSO_work/06_SL_to_PIVOT_to_Compare_with_WP/02_GJ_WP_2026-27/SL 2.0/BOTAD.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30326"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FF9C946E-B169-4FE6-9F91-9DF1233AB011}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9DB8F219-59CD-4722-A942-1F3BFAF68885}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -194,7 +194,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -226,6 +226,13 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="14"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="3">
     <fill>
@@ -419,9 +426,6 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -430,9 +434,6 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -466,6 +467,12 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -757,87 +764,87 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="25.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="17" t="s">
+      <c r="A1" s="15" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="17"/>
-      <c r="C1" s="17"/>
-      <c r="D1" s="17"/>
-      <c r="E1" s="17"/>
-      <c r="F1" s="17"/>
-      <c r="G1" s="17"/>
-      <c r="H1" s="17"/>
-      <c r="I1" s="17"/>
-      <c r="J1" s="17"/>
+      <c r="B1" s="15"/>
+      <c r="C1" s="15"/>
+      <c r="D1" s="15"/>
+      <c r="E1" s="15"/>
+      <c r="F1" s="15"/>
+      <c r="G1" s="15"/>
+      <c r="H1" s="15"/>
+      <c r="I1" s="15"/>
+      <c r="J1" s="15"/>
     </row>
     <row r="2" spans="1:10" ht="25.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="17" t="s">
+      <c r="A2" s="15" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="17"/>
-      <c r="C2" s="17"/>
-      <c r="D2" s="17"/>
-      <c r="E2" s="17"/>
-      <c r="F2" s="17"/>
-      <c r="G2" s="17"/>
-      <c r="H2" s="17"/>
-      <c r="I2" s="17"/>
-      <c r="J2" s="17"/>
+      <c r="B2" s="15"/>
+      <c r="C2" s="15"/>
+      <c r="D2" s="15"/>
+      <c r="E2" s="15"/>
+      <c r="F2" s="15"/>
+      <c r="G2" s="15"/>
+      <c r="H2" s="15"/>
+      <c r="I2" s="15"/>
+      <c r="J2" s="15"/>
     </row>
     <row r="3" spans="1:10" ht="25.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="18" t="s">
-        <v>2</v>
-      </c>
-      <c r="B3" s="19"/>
-      <c r="C3" s="19"/>
-      <c r="D3" s="19"/>
-      <c r="E3" s="19"/>
-      <c r="F3" s="19"/>
-      <c r="G3" s="19"/>
-      <c r="H3" s="19"/>
-      <c r="I3" s="19"/>
-      <c r="J3" s="20"/>
+      <c r="A3" s="16" t="s">
+        <v>2</v>
+      </c>
+      <c r="B3" s="17"/>
+      <c r="C3" s="17"/>
+      <c r="D3" s="17"/>
+      <c r="E3" s="17"/>
+      <c r="F3" s="17"/>
+      <c r="G3" s="17"/>
+      <c r="H3" s="17"/>
+      <c r="I3" s="17"/>
+      <c r="J3" s="18"/>
     </row>
     <row r="4" spans="1:10" ht="25.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="21" t="s">
+      <c r="A4" s="19" t="s">
         <v>5</v>
       </c>
-      <c r="B4" s="22"/>
+      <c r="B4" s="20"/>
       <c r="C4" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="D4" s="18">
+      <c r="D4" s="16">
         <v>6</v>
       </c>
-      <c r="E4" s="20"/>
-      <c r="F4" s="18" t="s">
+      <c r="E4" s="18"/>
+      <c r="F4" s="16" t="s">
         <v>48</v>
       </c>
-      <c r="G4" s="20"/>
-      <c r="H4" s="18">
+      <c r="G4" s="18"/>
+      <c r="H4" s="16">
         <v>6</v>
       </c>
-      <c r="I4" s="20"/>
+      <c r="I4" s="18"/>
       <c r="J4" s="2" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="5" spans="1:10" ht="25.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="23"/>
-      <c r="B5" s="24"/>
+      <c r="A5" s="21"/>
+      <c r="B5" s="22"/>
       <c r="C5" s="4"/>
-      <c r="D5" s="26" t="s">
+      <c r="D5" s="24" t="s">
         <v>12</v>
       </c>
-      <c r="E5" s="27"/>
-      <c r="F5" s="26" t="s">
+      <c r="E5" s="25"/>
+      <c r="F5" s="24" t="s">
         <v>13</v>
       </c>
-      <c r="G5" s="27"/>
-      <c r="H5" s="26" t="s">
-        <v>4</v>
-      </c>
-      <c r="I5" s="27"/>
+      <c r="G5" s="25"/>
+      <c r="H5" s="24" t="s">
+        <v>4</v>
+      </c>
+      <c r="I5" s="25"/>
       <c r="J5" s="2">
         <v>28</v>
       </c>
@@ -1006,11 +1013,11 @@
       </c>
     </row>
     <row r="12" spans="1:10" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="28" t="s">
+      <c r="A12" s="26" t="s">
         <v>23</v>
       </c>
-      <c r="B12" s="28"/>
-      <c r="C12" s="28"/>
+      <c r="B12" s="26"/>
+      <c r="C12" s="26"/>
       <c r="D12" s="2">
         <f>SUM(D7:D11)</f>
         <v>4</v>
@@ -1032,24 +1039,24 @@
       </c>
     </row>
     <row r="13" spans="1:10" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="25" t="s">
+      <c r="A13" s="23" t="s">
         <v>24</v>
       </c>
-      <c r="B13" s="25"/>
-      <c r="C13" s="25"/>
-      <c r="D13" s="25"/>
-      <c r="E13" s="25"/>
-      <c r="F13" s="25"/>
-      <c r="G13" s="25"/>
-      <c r="H13" s="25"/>
-      <c r="I13" s="25"/>
-      <c r="J13" s="25"/>
+      <c r="B13" s="23"/>
+      <c r="C13" s="23"/>
+      <c r="D13" s="23"/>
+      <c r="E13" s="23"/>
+      <c r="F13" s="23"/>
+      <c r="G13" s="23"/>
+      <c r="H13" s="23"/>
+      <c r="I13" s="23"/>
+      <c r="J13" s="23"/>
     </row>
     <row r="14" spans="1:10" ht="18" x14ac:dyDescent="0.3">
-      <c r="A14" s="14" t="s">
+      <c r="A14" s="13" t="s">
         <v>14</v>
       </c>
-      <c r="B14" s="14" t="s">
+      <c r="B14" s="13" t="s">
         <v>14</v>
       </c>
       <c r="C14" s="11" t="s">
@@ -1058,13 +1065,13 @@
       <c r="D14" s="11">
         <v>2</v>
       </c>
-      <c r="E14" s="12">
+      <c r="E14" s="28">
         <v>3</v>
       </c>
       <c r="F14" s="11">
         <v>2</v>
       </c>
-      <c r="G14" s="13">
+      <c r="G14" s="12">
         <v>6</v>
       </c>
       <c r="H14" s="11"/>
@@ -1075,10 +1082,10 @@
       </c>
     </row>
     <row r="15" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A15" s="14" t="s">
+      <c r="A15" s="13" t="s">
         <v>14</v>
       </c>
-      <c r="B15" s="14" t="s">
+      <c r="B15" s="13" t="s">
         <v>14</v>
       </c>
       <c r="C15" s="11" t="s">
@@ -1089,7 +1096,7 @@
       <c r="F15" s="11">
         <v>2</v>
       </c>
-      <c r="G15" s="13">
+      <c r="G15" s="12">
         <v>3</v>
       </c>
       <c r="H15" s="11"/>
@@ -1100,10 +1107,10 @@
       </c>
     </row>
     <row r="16" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A16" s="14" t="s">
+      <c r="A16" s="13" t="s">
         <v>14</v>
       </c>
-      <c r="B16" s="14" t="s">
+      <c r="B16" s="13" t="s">
         <v>14</v>
       </c>
       <c r="C16" s="11" t="s">
@@ -1114,7 +1121,7 @@
       <c r="F16" s="11">
         <v>2</v>
       </c>
-      <c r="G16" s="13">
+      <c r="G16" s="12">
         <v>5</v>
       </c>
       <c r="H16" s="11"/>
@@ -1125,10 +1132,10 @@
       </c>
     </row>
     <row r="17" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A17" s="14" t="s">
+      <c r="A17" s="13" t="s">
         <v>19</v>
       </c>
-      <c r="B17" s="14" t="s">
+      <c r="B17" s="13" t="s">
         <v>19</v>
       </c>
       <c r="C17" s="11" t="s">
@@ -1139,7 +1146,7 @@
       <c r="F17" s="11">
         <v>2</v>
       </c>
-      <c r="G17" s="13">
+      <c r="G17" s="12">
         <v>7</v>
       </c>
       <c r="H17" s="11"/>
@@ -1150,10 +1157,10 @@
       </c>
     </row>
     <row r="18" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A18" s="14" t="s">
+      <c r="A18" s="13" t="s">
         <v>19</v>
       </c>
-      <c r="B18" s="14" t="s">
+      <c r="B18" s="13" t="s">
         <v>19</v>
       </c>
       <c r="C18" s="11" t="s">
@@ -1164,7 +1171,7 @@
       <c r="F18" s="11">
         <v>2</v>
       </c>
-      <c r="G18" s="13">
+      <c r="G18" s="12">
         <v>4</v>
       </c>
       <c r="H18" s="11"/>
@@ -1175,10 +1182,10 @@
       </c>
     </row>
     <row r="19" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A19" s="14" t="s">
+      <c r="A19" s="13" t="s">
         <v>19</v>
       </c>
-      <c r="B19" s="14" t="s">
+      <c r="B19" s="13" t="s">
         <v>19</v>
       </c>
       <c r="C19" s="11" t="s">
@@ -1189,7 +1196,7 @@
       <c r="F19" s="11">
         <v>2</v>
       </c>
-      <c r="G19" s="13">
+      <c r="G19" s="12">
         <v>8</v>
       </c>
       <c r="H19" s="11"/>
@@ -1200,11 +1207,11 @@
       </c>
     </row>
     <row r="20" spans="1:10" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A20" s="18" t="s">
+      <c r="A20" s="16" t="s">
         <v>31</v>
       </c>
-      <c r="B20" s="19"/>
-      <c r="C20" s="20"/>
+      <c r="B20" s="17"/>
+      <c r="C20" s="18"/>
       <c r="D20" s="2">
         <f>SUM(D14:D19)</f>
         <v>2</v>
@@ -1226,11 +1233,11 @@
       </c>
     </row>
     <row r="21" spans="1:10" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A21" s="18" t="s">
+      <c r="A21" s="16" t="s">
         <v>32</v>
       </c>
-      <c r="B21" s="19"/>
-      <c r="C21" s="20"/>
+      <c r="B21" s="17"/>
+      <c r="C21" s="18"/>
       <c r="D21" s="2">
         <f>+D12+D20</f>
         <v>6</v>
@@ -1252,18 +1259,18 @@
       </c>
     </row>
     <row r="22" spans="1:10" ht="27" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A22" s="15" t="s">
+      <c r="A22" s="14" t="s">
         <v>51</v>
       </c>
-      <c r="B22" s="15"/>
-      <c r="C22" s="15"/>
-      <c r="D22" s="15"/>
-      <c r="E22" s="15"/>
-      <c r="F22" s="15"/>
-      <c r="G22" s="15"/>
-      <c r="H22" s="15"/>
-      <c r="I22" s="15"/>
-      <c r="J22" s="15"/>
+      <c r="B22" s="14"/>
+      <c r="C22" s="14"/>
+      <c r="D22" s="14"/>
+      <c r="E22" s="14"/>
+      <c r="F22" s="14"/>
+      <c r="G22" s="14"/>
+      <c r="H22" s="14"/>
+      <c r="I22" s="14"/>
+      <c r="J22" s="14"/>
     </row>
   </sheetData>
   <mergeCells count="15">
@@ -1284,6 +1291,7 @@
     <mergeCell ref="A12:C12"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -1293,87 +1301,87 @@
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row r="1" spans="1:10" ht="25.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="16" t="s">
+      <c r="A1" s="27" t="s">
         <v>41</v>
       </c>
-      <c r="B1" s="16"/>
-      <c r="C1" s="16"/>
-      <c r="D1" s="16"/>
-      <c r="E1" s="16"/>
-      <c r="F1" s="16"/>
-      <c r="G1" s="16"/>
-      <c r="H1" s="16"/>
-      <c r="I1" s="16"/>
-      <c r="J1" s="16"/>
+      <c r="B1" s="27"/>
+      <c r="C1" s="27"/>
+      <c r="D1" s="27"/>
+      <c r="E1" s="27"/>
+      <c r="F1" s="27"/>
+      <c r="G1" s="27"/>
+      <c r="H1" s="27"/>
+      <c r="I1" s="27"/>
+      <c r="J1" s="27"/>
     </row>
     <row r="2" spans="1:10" ht="25.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="17" t="s">
+      <c r="A2" s="15" t="s">
         <v>42</v>
       </c>
-      <c r="B2" s="17"/>
-      <c r="C2" s="17"/>
-      <c r="D2" s="17"/>
-      <c r="E2" s="17"/>
-      <c r="F2" s="17"/>
-      <c r="G2" s="17"/>
-      <c r="H2" s="17"/>
-      <c r="I2" s="17"/>
-      <c r="J2" s="17"/>
+      <c r="B2" s="15"/>
+      <c r="C2" s="15"/>
+      <c r="D2" s="15"/>
+      <c r="E2" s="15"/>
+      <c r="F2" s="15"/>
+      <c r="G2" s="15"/>
+      <c r="H2" s="15"/>
+      <c r="I2" s="15"/>
+      <c r="J2" s="15"/>
     </row>
     <row r="3" spans="1:10" ht="25.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="18" t="s">
-        <v>2</v>
-      </c>
-      <c r="B3" s="19"/>
-      <c r="C3" s="19"/>
-      <c r="D3" s="19"/>
-      <c r="E3" s="19"/>
-      <c r="F3" s="19"/>
-      <c r="G3" s="19"/>
-      <c r="H3" s="19"/>
-      <c r="I3" s="19"/>
-      <c r="J3" s="20"/>
+      <c r="A3" s="16" t="s">
+        <v>2</v>
+      </c>
+      <c r="B3" s="17"/>
+      <c r="C3" s="17"/>
+      <c r="D3" s="17"/>
+      <c r="E3" s="17"/>
+      <c r="F3" s="17"/>
+      <c r="G3" s="17"/>
+      <c r="H3" s="17"/>
+      <c r="I3" s="17"/>
+      <c r="J3" s="18"/>
     </row>
     <row r="4" spans="1:10" ht="25.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="21" t="s">
+      <c r="A4" s="19" t="s">
         <v>6</v>
       </c>
-      <c r="B4" s="22"/>
+      <c r="B4" s="20"/>
       <c r="C4" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="D4" s="18">
-        <v>4</v>
-      </c>
-      <c r="E4" s="20"/>
-      <c r="F4" s="18" t="s">
+      <c r="D4" s="16">
+        <v>4</v>
+      </c>
+      <c r="E4" s="18"/>
+      <c r="F4" s="16" t="s">
         <v>49</v>
       </c>
-      <c r="G4" s="20"/>
-      <c r="H4" s="18">
-        <v>4</v>
-      </c>
-      <c r="I4" s="20"/>
+      <c r="G4" s="18"/>
+      <c r="H4" s="16">
+        <v>4</v>
+      </c>
+      <c r="I4" s="18"/>
       <c r="J4" s="2" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="5" spans="1:10" ht="25.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="23"/>
-      <c r="B5" s="24"/>
+      <c r="A5" s="21"/>
+      <c r="B5" s="22"/>
       <c r="C5" s="4"/>
-      <c r="D5" s="26" t="s">
+      <c r="D5" s="24" t="s">
         <v>12</v>
       </c>
-      <c r="E5" s="27"/>
-      <c r="F5" s="26" t="s">
+      <c r="E5" s="25"/>
+      <c r="F5" s="24" t="s">
         <v>13</v>
       </c>
-      <c r="G5" s="27"/>
-      <c r="H5" s="26" t="s">
-        <v>4</v>
-      </c>
-      <c r="I5" s="27"/>
+      <c r="G5" s="25"/>
+      <c r="H5" s="24" t="s">
+        <v>4</v>
+      </c>
+      <c r="I5" s="25"/>
       <c r="J5" s="2">
         <v>20</v>
       </c>
@@ -1546,11 +1554,11 @@
       </c>
     </row>
     <row r="12" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A12" s="28" t="s">
+      <c r="A12" s="26" t="s">
         <v>23</v>
       </c>
-      <c r="B12" s="28"/>
-      <c r="C12" s="28"/>
+      <c r="B12" s="26"/>
+      <c r="C12" s="26"/>
       <c r="D12">
         <f>SUM(D7:D11)</f>
         <v>4</v>
@@ -1569,18 +1577,18 @@
       </c>
     </row>
     <row r="13" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A13" s="25" t="s">
+      <c r="A13" s="23" t="s">
         <v>24</v>
       </c>
-      <c r="B13" s="25"/>
-      <c r="C13" s="25"/>
-      <c r="D13" s="25"/>
-      <c r="E13" s="25"/>
-      <c r="F13" s="25"/>
-      <c r="G13" s="25"/>
-      <c r="H13" s="25"/>
-      <c r="I13" s="25"/>
-      <c r="J13" s="25"/>
+      <c r="B13" s="23"/>
+      <c r="C13" s="23"/>
+      <c r="D13" s="23"/>
+      <c r="E13" s="23"/>
+      <c r="F13" s="23"/>
+      <c r="G13" s="23"/>
+      <c r="H13" s="23"/>
+      <c r="I13" s="23"/>
+      <c r="J13" s="23"/>
     </row>
     <row r="14" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A14" s="7" t="s">
@@ -1597,7 +1605,7 @@
       <c r="F14" s="7">
         <v>2</v>
       </c>
-      <c r="G14" s="13">
+      <c r="G14" s="12">
         <v>5</v>
       </c>
       <c r="H14" s="7"/>
@@ -1622,7 +1630,7 @@
       <c r="F15" s="7">
         <v>2</v>
       </c>
-      <c r="G15" s="13">
+      <c r="G15" s="12">
         <v>6</v>
       </c>
       <c r="H15" s="7"/>
@@ -1633,11 +1641,11 @@
       </c>
     </row>
     <row r="16" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A16" s="18" t="s">
+      <c r="A16" s="16" t="s">
         <v>31</v>
       </c>
-      <c r="B16" s="19"/>
-      <c r="C16" s="20"/>
+      <c r="B16" s="17"/>
+      <c r="C16" s="18"/>
       <c r="D16" s="2">
         <f>SUM(D14:D15)</f>
         <v>0</v>
@@ -1659,11 +1667,11 @@
       </c>
     </row>
     <row r="17" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A17" s="18" t="s">
+      <c r="A17" s="16" t="s">
         <v>32</v>
       </c>
-      <c r="B17" s="19"/>
-      <c r="C17" s="20"/>
+      <c r="B17" s="17"/>
+      <c r="C17" s="18"/>
       <c r="D17" s="2">
         <f>+D12+D16</f>
         <v>4</v>
@@ -1685,18 +1693,18 @@
       </c>
     </row>
     <row r="18" spans="1:10" ht="35.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="15" t="s">
+      <c r="A18" s="14" t="s">
         <v>50</v>
       </c>
-      <c r="B18" s="15"/>
-      <c r="C18" s="15"/>
-      <c r="D18" s="15"/>
-      <c r="E18" s="15"/>
-      <c r="F18" s="15"/>
-      <c r="G18" s="15"/>
-      <c r="H18" s="15"/>
-      <c r="I18" s="15"/>
-      <c r="J18" s="15"/>
+      <c r="B18" s="14"/>
+      <c r="C18" s="14"/>
+      <c r="D18" s="14"/>
+      <c r="E18" s="14"/>
+      <c r="F18" s="14"/>
+      <c r="G18" s="14"/>
+      <c r="H18" s="14"/>
+      <c r="I18" s="14"/>
+      <c r="J18" s="14"/>
     </row>
   </sheetData>
   <mergeCells count="15">
